--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188911</v>
+        <v>113188845</v>
       </c>
       <c r="B2" t="n">
-        <v>78105</v>
+        <v>79185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545598</v>
+        <v>545634</v>
       </c>
       <c r="R2" t="n">
-        <v>7207729</v>
+        <v>7207917</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188902</v>
+        <v>113188904</v>
       </c>
       <c r="B3" t="n">
-        <v>90047</v>
+        <v>78121</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545601</v>
+        <v>545582</v>
       </c>
       <c r="R3" t="n">
-        <v>7207930</v>
+        <v>7207996</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188834</v>
+        <v>113188906</v>
       </c>
       <c r="B4" t="n">
-        <v>74286</v>
+        <v>78121</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545601</v>
+        <v>545636</v>
       </c>
       <c r="R4" t="n">
-        <v>7207647</v>
+        <v>7207923</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188833</v>
+        <v>113188913</v>
       </c>
       <c r="B5" t="n">
-        <v>77100</v>
+        <v>78121</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545680</v>
+        <v>545602</v>
       </c>
       <c r="R5" t="n">
-        <v>7207851</v>
+        <v>7207647</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
         <v>113188846</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188908</v>
+        <v>113188844</v>
       </c>
       <c r="B7" t="n">
-        <v>78105</v>
+        <v>79185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545682</v>
+        <v>545582</v>
       </c>
       <c r="R7" t="n">
-        <v>7207850</v>
+        <v>7207996</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188909</v>
+        <v>113188907</v>
       </c>
       <c r="B8" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545625</v>
+        <v>545658</v>
       </c>
       <c r="R8" t="n">
-        <v>7207808</v>
+        <v>7207904</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188913</v>
+        <v>113188929</v>
       </c>
       <c r="B9" t="n">
-        <v>78105</v>
+        <v>79217</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,20 +1471,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545602</v>
+        <v>545582</v>
       </c>
       <c r="R9" t="n">
-        <v>7207647</v>
+        <v>7207994</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,7 +1574,7 @@
         <v>113188847</v>
       </c>
       <c r="B10" t="n">
-        <v>74291</v>
+        <v>74307</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188912</v>
+        <v>113188833</v>
       </c>
       <c r="B11" t="n">
-        <v>78105</v>
+        <v>77116</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545588</v>
+        <v>545680</v>
       </c>
       <c r="R11" t="n">
-        <v>7207712</v>
+        <v>7207851</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188904</v>
+        <v>113188905</v>
       </c>
       <c r="B12" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545582</v>
+        <v>545601</v>
       </c>
       <c r="R12" t="n">
-        <v>7207996</v>
+        <v>7207930</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188849</v>
+        <v>113188854</v>
       </c>
       <c r="B13" t="n">
-        <v>77086</v>
+        <v>55976</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,34 +1923,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545602</v>
+        <v>545558</v>
       </c>
       <c r="R13" t="n">
-        <v>7207648</v>
+        <v>7207771</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188907</v>
+        <v>113188902</v>
       </c>
       <c r="B14" t="n">
-        <v>78105</v>
+        <v>90063</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545658</v>
+        <v>545601</v>
       </c>
       <c r="R14" t="n">
-        <v>7207904</v>
+        <v>7207930</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188906</v>
+        <v>113188840</v>
       </c>
       <c r="B15" t="n">
-        <v>78105</v>
+        <v>55984</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,38 +2147,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545636</v>
+        <v>545625</v>
       </c>
       <c r="R15" t="n">
-        <v>7207923</v>
+        <v>7207808</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188845</v>
+        <v>113188834</v>
       </c>
       <c r="B16" t="n">
-        <v>79169</v>
+        <v>74302</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2272,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545634</v>
+        <v>545601</v>
       </c>
       <c r="R16" t="n">
-        <v>7207917</v>
+        <v>7207647</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188905</v>
+        <v>113188842</v>
       </c>
       <c r="B17" t="n">
-        <v>78105</v>
+        <v>79211</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2380,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2408,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545601</v>
+        <v>545634</v>
       </c>
       <c r="R17" t="n">
-        <v>7207930</v>
+        <v>7207920</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2430,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188929</v>
+        <v>113188849</v>
       </c>
       <c r="B18" t="n">
-        <v>79201</v>
+        <v>77102</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,25 +2492,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2520,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545582</v>
+        <v>545602</v>
       </c>
       <c r="R18" t="n">
-        <v>7207994</v>
+        <v>7207648</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2542,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2592,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188900</v>
+        <v>113188909</v>
       </c>
       <c r="B19" t="n">
-        <v>74271</v>
+        <v>78121</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,25 +2604,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545658</v>
+        <v>545625</v>
       </c>
       <c r="R19" t="n">
-        <v>7207904</v>
+        <v>7207808</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2654,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188903</v>
+        <v>113188912</v>
       </c>
       <c r="B20" t="n">
-        <v>90047</v>
+        <v>78121</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,21 +2720,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545662</v>
+        <v>545588</v>
       </c>
       <c r="R20" t="n">
-        <v>7207897</v>
+        <v>7207712</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2766,7 +2779,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2789,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2816,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188844</v>
+        <v>113188911</v>
       </c>
       <c r="B21" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,21 +2832,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2856,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545582</v>
+        <v>545598</v>
       </c>
       <c r="R21" t="n">
-        <v>7207996</v>
+        <v>7207729</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2878,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188854</v>
+        <v>113188900</v>
       </c>
       <c r="B22" t="n">
-        <v>55976</v>
+        <v>74287</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2927,42 +2940,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6439</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545558</v>
+        <v>545658</v>
       </c>
       <c r="R22" t="n">
-        <v>7207771</v>
+        <v>7207904</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2994,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,10 +3040,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188840</v>
+        <v>113188908</v>
       </c>
       <c r="B23" t="n">
-        <v>55984</v>
+        <v>78121</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,47 +3052,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545625</v>
+        <v>545682</v>
       </c>
       <c r="R23" t="n">
-        <v>7207808</v>
+        <v>7207850</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188842</v>
+        <v>113188903</v>
       </c>
       <c r="B24" t="n">
-        <v>79195</v>
+        <v>90063</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3164,25 +3164,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545634</v>
+        <v>545662</v>
       </c>
       <c r="R24" t="n">
-        <v>7207920</v>
+        <v>7207897</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188845</v>
+        <v>113188904</v>
       </c>
       <c r="B2" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545634</v>
+        <v>545582</v>
       </c>
       <c r="R2" t="n">
-        <v>7207917</v>
+        <v>7207996</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188904</v>
+        <v>113188845</v>
       </c>
       <c r="B3" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545582</v>
+        <v>545634</v>
       </c>
       <c r="R3" t="n">
-        <v>7207996</v>
+        <v>7207917</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188904</v>
+        <v>113188911</v>
       </c>
       <c r="B2" t="n">
         <v>78121</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545582</v>
+        <v>545598</v>
       </c>
       <c r="R2" t="n">
-        <v>7207996</v>
+        <v>7207729</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188845</v>
+        <v>113188903</v>
       </c>
       <c r="B3" t="n">
-        <v>79185</v>
+        <v>90063</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545634</v>
+        <v>545662</v>
       </c>
       <c r="R3" t="n">
-        <v>7207917</v>
+        <v>7207897</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188906</v>
+        <v>113188845</v>
       </c>
       <c r="B4" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545636</v>
+        <v>545634</v>
       </c>
       <c r="R4" t="n">
-        <v>7207923</v>
+        <v>7207917</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188913</v>
+        <v>113188900</v>
       </c>
       <c r="B5" t="n">
-        <v>78121</v>
+        <v>74287</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545602</v>
+        <v>545658</v>
       </c>
       <c r="R5" t="n">
-        <v>7207647</v>
+        <v>7207904</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188846</v>
+        <v>113188906</v>
       </c>
       <c r="B6" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545592</v>
+        <v>545636</v>
       </c>
       <c r="R6" t="n">
-        <v>7207729</v>
+        <v>7207923</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188844</v>
+        <v>113188847</v>
       </c>
       <c r="B7" t="n">
-        <v>79185</v>
+        <v>74307</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545582</v>
+        <v>545589</v>
       </c>
       <c r="R7" t="n">
-        <v>7207996</v>
+        <v>7207713</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188907</v>
+        <v>113188846</v>
       </c>
       <c r="B8" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545658</v>
+        <v>545592</v>
       </c>
       <c r="R8" t="n">
-        <v>7207904</v>
+        <v>7207729</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188929</v>
+        <v>113188907</v>
       </c>
       <c r="B9" t="n">
-        <v>79217</v>
+        <v>78121</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,20 +1471,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545582</v>
+        <v>545658</v>
       </c>
       <c r="R9" t="n">
-        <v>7207994</v>
+        <v>7207904</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188847</v>
+        <v>113188904</v>
       </c>
       <c r="B10" t="n">
-        <v>74307</v>
+        <v>78121</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545589</v>
+        <v>545582</v>
       </c>
       <c r="R10" t="n">
-        <v>7207713</v>
+        <v>7207996</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188833</v>
+        <v>113188840</v>
       </c>
       <c r="B11" t="n">
-        <v>77116</v>
+        <v>55984</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,38 +1695,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>314</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545680</v>
+        <v>545625</v>
       </c>
       <c r="R11" t="n">
-        <v>7207851</v>
+        <v>7207808</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188905</v>
+        <v>113188929</v>
       </c>
       <c r="B12" t="n">
-        <v>78121</v>
+        <v>79217</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,20 +1816,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1835,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545601</v>
+        <v>545582</v>
       </c>
       <c r="R12" t="n">
-        <v>7207930</v>
+        <v>7207994</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188854</v>
+        <v>113188909</v>
       </c>
       <c r="B13" t="n">
-        <v>55976</v>
+        <v>78121</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,38 +1932,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545558</v>
+        <v>545625</v>
       </c>
       <c r="R13" t="n">
-        <v>7207771</v>
+        <v>7207808</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1986,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188902</v>
+        <v>113188912</v>
       </c>
       <c r="B14" t="n">
-        <v>90063</v>
+        <v>78121</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,21 +2044,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545601</v>
+        <v>545588</v>
       </c>
       <c r="R14" t="n">
-        <v>7207930</v>
+        <v>7207712</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2098,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188840</v>
+        <v>113188844</v>
       </c>
       <c r="B15" t="n">
-        <v>55984</v>
+        <v>79185</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,47 +2152,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545625</v>
+        <v>545582</v>
       </c>
       <c r="R15" t="n">
-        <v>7207808</v>
+        <v>7207996</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2219,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2368,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188842</v>
+        <v>113188854</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>55976</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2380,38 +2376,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545634</v>
+        <v>545558</v>
       </c>
       <c r="R17" t="n">
-        <v>7207920</v>
+        <v>7207771</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188849</v>
+        <v>113188905</v>
       </c>
       <c r="B18" t="n">
-        <v>77102</v>
+        <v>78121</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545602</v>
+        <v>545601</v>
       </c>
       <c r="R18" t="n">
-        <v>7207648</v>
+        <v>7207930</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188909</v>
+        <v>113188842</v>
       </c>
       <c r="B19" t="n">
-        <v>78121</v>
+        <v>79211</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,25 +2604,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545625</v>
+        <v>545634</v>
       </c>
       <c r="R19" t="n">
-        <v>7207808</v>
+        <v>7207920</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188912</v>
+        <v>113188902</v>
       </c>
       <c r="B20" t="n">
-        <v>78121</v>
+        <v>90063</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2720,21 +2720,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545588</v>
+        <v>545601</v>
       </c>
       <c r="R20" t="n">
-        <v>7207712</v>
+        <v>7207930</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,7 +2816,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188911</v>
+        <v>113188913</v>
       </c>
       <c r="B21" t="n">
         <v>78121</v>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545598</v>
+        <v>545602</v>
       </c>
       <c r="R21" t="n">
-        <v>7207729</v>
+        <v>7207647</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188900</v>
+        <v>113188833</v>
       </c>
       <c r="B22" t="n">
-        <v>74287</v>
+        <v>77116</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,25 +2940,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6439</v>
+        <v>314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545658</v>
+        <v>545680</v>
       </c>
       <c r="R22" t="n">
-        <v>7207904</v>
+        <v>7207851</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,10 +3040,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188908</v>
+        <v>113188849</v>
       </c>
       <c r="B23" t="n">
-        <v>78121</v>
+        <v>77102</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545682</v>
+        <v>545602</v>
       </c>
       <c r="R23" t="n">
-        <v>7207850</v>
+        <v>7207648</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188903</v>
+        <v>113188908</v>
       </c>
       <c r="B24" t="n">
-        <v>90063</v>
+        <v>78121</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3168,21 +3168,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545662</v>
+        <v>545682</v>
       </c>
       <c r="R24" t="n">
-        <v>7207897</v>
+        <v>7207850</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188911</v>
+        <v>113188846</v>
       </c>
       <c r="B2" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545598</v>
+        <v>545592</v>
       </c>
       <c r="R2" t="n">
         <v>7207729</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188903</v>
+        <v>113188900</v>
       </c>
       <c r="B3" t="n">
-        <v>90063</v>
+        <v>74299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545662</v>
+        <v>545658</v>
       </c>
       <c r="R3" t="n">
-        <v>7207897</v>
+        <v>7207904</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188845</v>
+        <v>113188908</v>
       </c>
       <c r="B4" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545634</v>
+        <v>545682</v>
       </c>
       <c r="R4" t="n">
-        <v>7207917</v>
+        <v>7207850</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188900</v>
+        <v>113188840</v>
       </c>
       <c r="B5" t="n">
-        <v>74287</v>
+        <v>55985</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545658</v>
+        <v>545625</v>
       </c>
       <c r="R5" t="n">
-        <v>7207904</v>
+        <v>7207808</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188906</v>
+        <v>113188844</v>
       </c>
       <c r="B6" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545636</v>
+        <v>545582</v>
       </c>
       <c r="R6" t="n">
-        <v>7207923</v>
+        <v>7207996</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188847</v>
+        <v>113188845</v>
       </c>
       <c r="B7" t="n">
-        <v>74307</v>
+        <v>79197</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545589</v>
+        <v>545634</v>
       </c>
       <c r="R7" t="n">
-        <v>7207713</v>
+        <v>7207917</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188846</v>
+        <v>113188909</v>
       </c>
       <c r="B8" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1372,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545592</v>
+        <v>545625</v>
       </c>
       <c r="R8" t="n">
-        <v>7207729</v>
+        <v>7207808</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188907</v>
+        <v>113188902</v>
       </c>
       <c r="B9" t="n">
-        <v>78121</v>
+        <v>90075</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545658</v>
+        <v>545601</v>
       </c>
       <c r="R9" t="n">
-        <v>7207904</v>
+        <v>7207930</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188904</v>
+        <v>113188833</v>
       </c>
       <c r="B10" t="n">
-        <v>78121</v>
+        <v>77128</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1596,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545582</v>
+        <v>545680</v>
       </c>
       <c r="R10" t="n">
-        <v>7207996</v>
+        <v>7207851</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188840</v>
+        <v>113188907</v>
       </c>
       <c r="B11" t="n">
-        <v>55984</v>
+        <v>78133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,47 +1704,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545625</v>
+        <v>545658</v>
       </c>
       <c r="R11" t="n">
-        <v>7207808</v>
+        <v>7207904</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188929</v>
+        <v>113188849</v>
       </c>
       <c r="B12" t="n">
-        <v>79217</v>
+        <v>77114</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,25 +1816,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545582</v>
+        <v>545602</v>
       </c>
       <c r="R12" t="n">
-        <v>7207994</v>
+        <v>7207648</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188909</v>
+        <v>113188905</v>
       </c>
       <c r="B13" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545625</v>
+        <v>545601</v>
       </c>
       <c r="R13" t="n">
-        <v>7207808</v>
+        <v>7207930</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188912</v>
+        <v>113188911</v>
       </c>
       <c r="B14" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545588</v>
+        <v>545598</v>
       </c>
       <c r="R14" t="n">
-        <v>7207712</v>
+        <v>7207729</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188844</v>
+        <v>113188929</v>
       </c>
       <c r="B15" t="n">
-        <v>79185</v>
+        <v>79229</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,25 +2152,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
         <v>545582</v>
       </c>
       <c r="R15" t="n">
-        <v>7207996</v>
+        <v>7207994</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188834</v>
+        <v>113188854</v>
       </c>
       <c r="B16" t="n">
-        <v>74302</v>
+        <v>55977</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,34 +2268,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545601</v>
+        <v>545558</v>
       </c>
       <c r="R16" t="n">
-        <v>7207647</v>
+        <v>7207771</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188854</v>
+        <v>113188847</v>
       </c>
       <c r="B17" t="n">
-        <v>55976</v>
+        <v>74319</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2380,38 +2384,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>1467</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545558</v>
+        <v>545589</v>
       </c>
       <c r="R17" t="n">
-        <v>7207771</v>
+        <v>7207713</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188905</v>
+        <v>113188842</v>
       </c>
       <c r="B18" t="n">
-        <v>78121</v>
+        <v>79223</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,25 +2492,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545601</v>
+        <v>545634</v>
       </c>
       <c r="R18" t="n">
-        <v>7207930</v>
+        <v>7207920</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188842</v>
+        <v>113188913</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>78133</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,25 +2604,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545634</v>
+        <v>545602</v>
       </c>
       <c r="R19" t="n">
-        <v>7207920</v>
+        <v>7207647</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188902</v>
+        <v>113188903</v>
       </c>
       <c r="B20" t="n">
-        <v>90063</v>
+        <v>90075</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545601</v>
+        <v>545662</v>
       </c>
       <c r="R20" t="n">
-        <v>7207930</v>
+        <v>7207897</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,10 +2816,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188913</v>
+        <v>113188912</v>
       </c>
       <c r="B21" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545602</v>
+        <v>545588</v>
       </c>
       <c r="R21" t="n">
-        <v>7207647</v>
+        <v>7207712</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188833</v>
+        <v>113188906</v>
       </c>
       <c r="B22" t="n">
-        <v>77116</v>
+        <v>78133</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2944,21 +2944,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545680</v>
+        <v>545636</v>
       </c>
       <c r="R22" t="n">
-        <v>7207851</v>
+        <v>7207923</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,10 +3040,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188849</v>
+        <v>113188904</v>
       </c>
       <c r="B23" t="n">
-        <v>77102</v>
+        <v>78133</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545602</v>
+        <v>545582</v>
       </c>
       <c r="R23" t="n">
-        <v>7207648</v>
+        <v>7207996</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188908</v>
+        <v>113188834</v>
       </c>
       <c r="B24" t="n">
-        <v>78121</v>
+        <v>74314</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3168,21 +3168,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545682</v>
+        <v>545601</v>
       </c>
       <c r="R24" t="n">
-        <v>7207850</v>
+        <v>7207647</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188846</v>
+        <v>113188906</v>
       </c>
       <c r="B2" t="n">
-        <v>79197</v>
+        <v>78133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545592</v>
+        <v>545636</v>
       </c>
       <c r="R2" t="n">
-        <v>7207729</v>
+        <v>7207923</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188900</v>
+        <v>113188846</v>
       </c>
       <c r="B3" t="n">
-        <v>74299</v>
+        <v>79197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545658</v>
+        <v>545592</v>
       </c>
       <c r="R3" t="n">
-        <v>7207904</v>
+        <v>7207729</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188908</v>
+        <v>113188849</v>
       </c>
       <c r="B4" t="n">
-        <v>78133</v>
+        <v>77114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545682</v>
+        <v>545602</v>
       </c>
       <c r="R4" t="n">
-        <v>7207850</v>
+        <v>7207648</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188840</v>
+        <v>113188905</v>
       </c>
       <c r="B5" t="n">
-        <v>55985</v>
+        <v>78133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,47 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545625</v>
+        <v>545601</v>
       </c>
       <c r="R5" t="n">
-        <v>7207808</v>
+        <v>7207930</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188844</v>
+        <v>113188909</v>
       </c>
       <c r="B6" t="n">
-        <v>79197</v>
+        <v>78133</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545582</v>
+        <v>545625</v>
       </c>
       <c r="R6" t="n">
-        <v>7207996</v>
+        <v>7207808</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1207,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188845</v>
+        <v>113188842</v>
       </c>
       <c r="B7" t="n">
-        <v>79197</v>
+        <v>79223</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,7 +1278,7 @@
         <v>545634</v>
       </c>
       <c r="R7" t="n">
-        <v>7207917</v>
+        <v>7207920</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1356,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188909</v>
+        <v>113188834</v>
       </c>
       <c r="B8" t="n">
-        <v>78133</v>
+        <v>74314</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545625</v>
+        <v>545601</v>
       </c>
       <c r="R8" t="n">
-        <v>7207808</v>
+        <v>7207647</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1431,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188902</v>
+        <v>113188913</v>
       </c>
       <c r="B9" t="n">
-        <v>90075</v>
+        <v>78133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545601</v>
+        <v>545602</v>
       </c>
       <c r="R9" t="n">
-        <v>7207930</v>
+        <v>7207647</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188833</v>
+        <v>113188911</v>
       </c>
       <c r="B10" t="n">
-        <v>77128</v>
+        <v>78133</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545680</v>
+        <v>545598</v>
       </c>
       <c r="R10" t="n">
-        <v>7207851</v>
+        <v>7207729</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188907</v>
+        <v>113188847</v>
       </c>
       <c r="B11" t="n">
-        <v>78133</v>
+        <v>74319</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545658</v>
+        <v>545589</v>
       </c>
       <c r="R11" t="n">
-        <v>7207904</v>
+        <v>7207713</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188849</v>
+        <v>113188903</v>
       </c>
       <c r="B12" t="n">
-        <v>77114</v>
+        <v>90075</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545602</v>
+        <v>545662</v>
       </c>
       <c r="R12" t="n">
-        <v>7207648</v>
+        <v>7207897</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188905</v>
+        <v>113188912</v>
       </c>
       <c r="B13" t="n">
         <v>78133</v>
@@ -1956,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545601</v>
+        <v>545588</v>
       </c>
       <c r="R13" t="n">
-        <v>7207930</v>
+        <v>7207712</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188911</v>
+        <v>113188854</v>
       </c>
       <c r="B14" t="n">
-        <v>78133</v>
+        <v>55977</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,34 +2035,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545598</v>
+        <v>545558</v>
       </c>
       <c r="R14" t="n">
-        <v>7207729</v>
+        <v>7207771</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188929</v>
+        <v>113188844</v>
       </c>
       <c r="B15" t="n">
-        <v>79229</v>
+        <v>79197</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,25 +2147,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2183,7 +2178,7 @@
         <v>545582</v>
       </c>
       <c r="R15" t="n">
-        <v>7207994</v>
+        <v>7207996</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2252,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188854</v>
+        <v>113188902</v>
       </c>
       <c r="B16" t="n">
-        <v>55977</v>
+        <v>90075</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,38 +2263,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545558</v>
+        <v>545601</v>
       </c>
       <c r="R16" t="n">
-        <v>7207771</v>
+        <v>7207930</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2331,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188847</v>
+        <v>113188833</v>
       </c>
       <c r="B17" t="n">
-        <v>74319</v>
+        <v>77128</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,21 +2375,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1467</v>
+        <v>314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2408,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545589</v>
+        <v>545680</v>
       </c>
       <c r="R17" t="n">
-        <v>7207713</v>
+        <v>7207851</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2443,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188842</v>
+        <v>113188845</v>
       </c>
       <c r="B18" t="n">
-        <v>79223</v>
+        <v>79197</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,25 +2483,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2523,7 +2514,7 @@
         <v>545634</v>
       </c>
       <c r="R18" t="n">
-        <v>7207920</v>
+        <v>7207917</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2592,7 +2583,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188913</v>
+        <v>113188908</v>
       </c>
       <c r="B19" t="n">
         <v>78133</v>
@@ -2632,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545602</v>
+        <v>545682</v>
       </c>
       <c r="R19" t="n">
-        <v>7207647</v>
+        <v>7207850</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2667,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2668,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188903</v>
+        <v>113188900</v>
       </c>
       <c r="B20" t="n">
-        <v>90075</v>
+        <v>74299</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2716,25 +2707,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2744,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545662</v>
+        <v>545658</v>
       </c>
       <c r="R20" t="n">
-        <v>7207897</v>
+        <v>7207904</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2816,10 +2807,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188912</v>
+        <v>113188840</v>
       </c>
       <c r="B21" t="n">
-        <v>78133</v>
+        <v>55985</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2828,38 +2819,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545588</v>
+        <v>545625</v>
       </c>
       <c r="R21" t="n">
-        <v>7207712</v>
+        <v>7207808</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188906</v>
+        <v>113188929</v>
       </c>
       <c r="B22" t="n">
-        <v>78133</v>
+        <v>79229</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,20 +2940,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545636</v>
+        <v>545582</v>
       </c>
       <c r="R22" t="n">
-        <v>7207923</v>
+        <v>7207994</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3152,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188834</v>
+        <v>113188907</v>
       </c>
       <c r="B24" t="n">
-        <v>74314</v>
+        <v>78133</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3168,21 +3168,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545601</v>
+        <v>545658</v>
       </c>
       <c r="R24" t="n">
-        <v>7207647</v>
+        <v>7207904</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188854</v>
+        <v>113188844</v>
       </c>
       <c r="B14" t="n">
-        <v>55977</v>
+        <v>79197</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,38 +2035,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545558</v>
+        <v>545582</v>
       </c>
       <c r="R14" t="n">
-        <v>7207771</v>
+        <v>7207996</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2098,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188844</v>
+        <v>113188902</v>
       </c>
       <c r="B15" t="n">
-        <v>79197</v>
+        <v>90075</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545582</v>
+        <v>545601</v>
       </c>
       <c r="R15" t="n">
-        <v>7207996</v>
+        <v>7207930</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2210,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188902</v>
+        <v>113188854</v>
       </c>
       <c r="B16" t="n">
-        <v>90075</v>
+        <v>55977</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,34 +2259,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545601</v>
+        <v>545558</v>
       </c>
       <c r="R16" t="n">
-        <v>7207930</v>
+        <v>7207771</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188906</v>
+        <v>113188902</v>
       </c>
       <c r="B2" t="n">
-        <v>78133</v>
+        <v>90097</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545636</v>
+        <v>545601</v>
       </c>
       <c r="R2" t="n">
-        <v>7207923</v>
+        <v>7207930</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188846</v>
+        <v>113188834</v>
       </c>
       <c r="B3" t="n">
-        <v>79197</v>
+        <v>74336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545592</v>
+        <v>545601</v>
       </c>
       <c r="R3" t="n">
-        <v>7207729</v>
+        <v>7207647</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188849</v>
+        <v>113188904</v>
       </c>
       <c r="B4" t="n">
-        <v>77114</v>
+        <v>78155</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545602</v>
+        <v>545582</v>
       </c>
       <c r="R4" t="n">
-        <v>7207648</v>
+        <v>7207996</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188905</v>
+        <v>113188911</v>
       </c>
       <c r="B5" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545601</v>
+        <v>545598</v>
       </c>
       <c r="R5" t="n">
-        <v>7207930</v>
+        <v>7207729</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188909</v>
+        <v>113188844</v>
       </c>
       <c r="B6" t="n">
-        <v>78133</v>
+        <v>79219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545625</v>
+        <v>545582</v>
       </c>
       <c r="R6" t="n">
-        <v>7207808</v>
+        <v>7207996</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188842</v>
+        <v>113188847</v>
       </c>
       <c r="B7" t="n">
-        <v>79223</v>
+        <v>74341</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545634</v>
+        <v>545589</v>
       </c>
       <c r="R7" t="n">
-        <v>7207920</v>
+        <v>7207713</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188834</v>
+        <v>113188912</v>
       </c>
       <c r="B8" t="n">
-        <v>74314</v>
+        <v>78155</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545601</v>
+        <v>545588</v>
       </c>
       <c r="R8" t="n">
-        <v>7207647</v>
+        <v>7207712</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188913</v>
+        <v>113188900</v>
       </c>
       <c r="B9" t="n">
-        <v>78133</v>
+        <v>74321</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545602</v>
+        <v>545658</v>
       </c>
       <c r="R9" t="n">
-        <v>7207647</v>
+        <v>7207904</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188911</v>
+        <v>113188854</v>
       </c>
       <c r="B10" t="n">
-        <v>78133</v>
+        <v>55977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,34 +1587,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545598</v>
+        <v>545558</v>
       </c>
       <c r="R10" t="n">
-        <v>7207729</v>
+        <v>7207771</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188847</v>
+        <v>113188929</v>
       </c>
       <c r="B11" t="n">
-        <v>74319</v>
+        <v>79251</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1699,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1467</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545589</v>
+        <v>545582</v>
       </c>
       <c r="R11" t="n">
-        <v>7207713</v>
+        <v>7207994</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188903</v>
+        <v>113188849</v>
       </c>
       <c r="B12" t="n">
-        <v>90075</v>
+        <v>77136</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1815,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545662</v>
+        <v>545602</v>
       </c>
       <c r="R12" t="n">
-        <v>7207897</v>
+        <v>7207648</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188912</v>
+        <v>113188905</v>
       </c>
       <c r="B13" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545588</v>
+        <v>545601</v>
       </c>
       <c r="R13" t="n">
-        <v>7207712</v>
+        <v>7207930</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188844</v>
+        <v>113188903</v>
       </c>
       <c r="B14" t="n">
-        <v>79197</v>
+        <v>90097</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545582</v>
+        <v>545662</v>
       </c>
       <c r="R14" t="n">
-        <v>7207996</v>
+        <v>7207897</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188902</v>
+        <v>113188906</v>
       </c>
       <c r="B15" t="n">
-        <v>90075</v>
+        <v>78155</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2151,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545601</v>
+        <v>545636</v>
       </c>
       <c r="R15" t="n">
-        <v>7207930</v>
+        <v>7207923</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188854</v>
+        <v>113188913</v>
       </c>
       <c r="B16" t="n">
-        <v>55977</v>
+        <v>78155</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,38 +2263,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545558</v>
+        <v>545602</v>
       </c>
       <c r="R16" t="n">
-        <v>7207771</v>
+        <v>7207647</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,7 +2362,7 @@
         <v>113188833</v>
       </c>
       <c r="B17" t="n">
-        <v>77128</v>
+        <v>77150</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2471,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188845</v>
+        <v>113188907</v>
       </c>
       <c r="B18" t="n">
-        <v>79197</v>
+        <v>78155</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2487,21 +2487,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545634</v>
+        <v>545658</v>
       </c>
       <c r="R18" t="n">
-        <v>7207917</v>
+        <v>7207904</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188908</v>
+        <v>113188846</v>
       </c>
       <c r="B19" t="n">
-        <v>78133</v>
+        <v>79219</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545682</v>
+        <v>545592</v>
       </c>
       <c r="R19" t="n">
-        <v>7207850</v>
+        <v>7207729</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188900</v>
+        <v>113188908</v>
       </c>
       <c r="B20" t="n">
-        <v>74299</v>
+        <v>78155</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545658</v>
+        <v>545682</v>
       </c>
       <c r="R20" t="n">
-        <v>7207904</v>
+        <v>7207850</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2928,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188929</v>
+        <v>113188909</v>
       </c>
       <c r="B22" t="n">
-        <v>79229</v>
+        <v>78155</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,20 +2940,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545582</v>
+        <v>545625</v>
       </c>
       <c r="R22" t="n">
-        <v>7207994</v>
+        <v>7207808</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,10 +3040,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188904</v>
+        <v>113188845</v>
       </c>
       <c r="B23" t="n">
-        <v>78133</v>
+        <v>79219</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545582</v>
+        <v>545634</v>
       </c>
       <c r="R23" t="n">
-        <v>7207996</v>
+        <v>7207917</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188907</v>
+        <v>113188842</v>
       </c>
       <c r="B24" t="n">
-        <v>78133</v>
+        <v>79245</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3164,25 +3164,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545658</v>
+        <v>545634</v>
       </c>
       <c r="R24" t="n">
-        <v>7207904</v>
+        <v>7207920</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -2359,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188833</v>
+        <v>113188907</v>
       </c>
       <c r="B17" t="n">
-        <v>77150</v>
+        <v>78155</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2375,21 +2375,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545680</v>
+        <v>545658</v>
       </c>
       <c r="R17" t="n">
-        <v>7207851</v>
+        <v>7207904</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188907</v>
+        <v>113188833</v>
       </c>
       <c r="B18" t="n">
-        <v>78155</v>
+        <v>77150</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2487,21 +2487,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545658</v>
+        <v>545680</v>
       </c>
       <c r="R18" t="n">
-        <v>7207904</v>
+        <v>7207851</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188902</v>
+        <v>113188844</v>
       </c>
       <c r="B2" t="n">
-        <v>90097</v>
+        <v>79223</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545601</v>
+        <v>545582</v>
       </c>
       <c r="R2" t="n">
-        <v>7207930</v>
+        <v>7207996</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188834</v>
+        <v>113188854</v>
       </c>
       <c r="B3" t="n">
-        <v>74336</v>
+        <v>55980</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545601</v>
+        <v>545558</v>
       </c>
       <c r="R3" t="n">
-        <v>7207647</v>
+        <v>7207771</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188904</v>
+        <v>113188849</v>
       </c>
       <c r="B4" t="n">
-        <v>78155</v>
+        <v>77139</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545582</v>
+        <v>545602</v>
       </c>
       <c r="R4" t="n">
-        <v>7207996</v>
+        <v>7207648</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188911</v>
+        <v>113188903</v>
       </c>
       <c r="B5" t="n">
-        <v>78155</v>
+        <v>90101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545598</v>
+        <v>545662</v>
       </c>
       <c r="R5" t="n">
-        <v>7207729</v>
+        <v>7207897</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188844</v>
+        <v>113188904</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>78158</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1235,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188847</v>
+        <v>113188912</v>
       </c>
       <c r="B7" t="n">
-        <v>74341</v>
+        <v>78158</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545589</v>
+        <v>545588</v>
       </c>
       <c r="R7" t="n">
-        <v>7207713</v>
+        <v>7207712</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1347,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188912</v>
+        <v>113188846</v>
       </c>
       <c r="B8" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545588</v>
+        <v>545592</v>
       </c>
       <c r="R8" t="n">
-        <v>7207712</v>
+        <v>7207729</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188900</v>
+        <v>113188911</v>
       </c>
       <c r="B9" t="n">
-        <v>74321</v>
+        <v>78158</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1475,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545658</v>
+        <v>545598</v>
       </c>
       <c r="R9" t="n">
-        <v>7207904</v>
+        <v>7207729</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188854</v>
+        <v>113188833</v>
       </c>
       <c r="B10" t="n">
-        <v>55977</v>
+        <v>77153</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,38 +1591,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545558</v>
+        <v>545680</v>
       </c>
       <c r="R10" t="n">
-        <v>7207771</v>
+        <v>7207851</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188929</v>
+        <v>113188834</v>
       </c>
       <c r="B11" t="n">
-        <v>79251</v>
+        <v>74339</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,25 +1699,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545582</v>
+        <v>545601</v>
       </c>
       <c r="R11" t="n">
-        <v>7207994</v>
+        <v>7207647</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188849</v>
+        <v>113188840</v>
       </c>
       <c r="B12" t="n">
-        <v>77136</v>
+        <v>55988</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,38 +1811,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545602</v>
+        <v>545625</v>
       </c>
       <c r="R12" t="n">
-        <v>7207648</v>
+        <v>7207808</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1874,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1884,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188905</v>
+        <v>113188902</v>
       </c>
       <c r="B13" t="n">
-        <v>78155</v>
+        <v>90101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1927,21 +1936,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2023,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188903</v>
+        <v>113188907</v>
       </c>
       <c r="B14" t="n">
-        <v>90097</v>
+        <v>78158</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,21 +2048,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2072,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545662</v>
+        <v>545658</v>
       </c>
       <c r="R14" t="n">
-        <v>7207897</v>
+        <v>7207904</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2135,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188906</v>
+        <v>113188900</v>
       </c>
       <c r="B15" t="n">
-        <v>78155</v>
+        <v>74324</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,25 +2156,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2175,10 +2184,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545636</v>
+        <v>545658</v>
       </c>
       <c r="R15" t="n">
-        <v>7207923</v>
+        <v>7207904</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2210,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2220,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188913</v>
+        <v>113188842</v>
       </c>
       <c r="B16" t="n">
-        <v>78155</v>
+        <v>79249</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,25 +2268,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2287,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545602</v>
+        <v>545634</v>
       </c>
       <c r="R16" t="n">
-        <v>7207647</v>
+        <v>7207920</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2322,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188907</v>
+        <v>113188909</v>
       </c>
       <c r="B17" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,10 +2408,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545658</v>
+        <v>545625</v>
       </c>
       <c r="R17" t="n">
-        <v>7207904</v>
+        <v>7207808</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2434,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188833</v>
+        <v>113188847</v>
       </c>
       <c r="B18" t="n">
-        <v>77150</v>
+        <v>74344</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2487,21 +2496,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>314</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2511,10 +2520,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545680</v>
+        <v>545589</v>
       </c>
       <c r="R18" t="n">
-        <v>7207851</v>
+        <v>7207713</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2546,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2592,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188846</v>
+        <v>113188906</v>
       </c>
       <c r="B19" t="n">
-        <v>79219</v>
+        <v>78158</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,21 +2608,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545592</v>
+        <v>545636</v>
       </c>
       <c r="R19" t="n">
-        <v>7207729</v>
+        <v>7207923</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2658,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,7 +2707,7 @@
         <v>113188908</v>
       </c>
       <c r="B20" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2807,10 +2816,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188840</v>
+        <v>113188845</v>
       </c>
       <c r="B21" t="n">
-        <v>55985</v>
+        <v>79223</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,47 +2828,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545625</v>
+        <v>545634</v>
       </c>
       <c r="R21" t="n">
-        <v>7207808</v>
+        <v>7207917</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188909</v>
+        <v>113188929</v>
       </c>
       <c r="B22" t="n">
-        <v>78155</v>
+        <v>79255</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,20 +2940,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545625</v>
+        <v>545582</v>
       </c>
       <c r="R22" t="n">
-        <v>7207808</v>
+        <v>7207994</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,10 +3040,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188845</v>
+        <v>113188913</v>
       </c>
       <c r="B23" t="n">
-        <v>79219</v>
+        <v>78158</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545634</v>
+        <v>545602</v>
       </c>
       <c r="R23" t="n">
-        <v>7207917</v>
+        <v>7207647</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188842</v>
+        <v>113188905</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>78158</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3164,25 +3164,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545634</v>
+        <v>545601</v>
       </c>
       <c r="R24" t="n">
-        <v>7207920</v>
+        <v>7207930</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188844</v>
+        <v>113188854</v>
       </c>
       <c r="B2" t="n">
-        <v>79223</v>
+        <v>55980</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545582</v>
+        <v>545558</v>
       </c>
       <c r="R2" t="n">
-        <v>7207996</v>
+        <v>7207771</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188854</v>
+        <v>113188844</v>
       </c>
       <c r="B3" t="n">
-        <v>55980</v>
+        <v>79223</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545558</v>
+        <v>545582</v>
       </c>
       <c r="R3" t="n">
-        <v>7207771</v>
+        <v>7207996</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188849</v>
+        <v>113188903</v>
       </c>
       <c r="B4" t="n">
-        <v>77139</v>
+        <v>90101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545602</v>
+        <v>545662</v>
       </c>
       <c r="R4" t="n">
-        <v>7207648</v>
+        <v>7207897</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113188903</v>
+        <v>113188849</v>
       </c>
       <c r="B5" t="n">
-        <v>90101</v>
+        <v>77139</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545662</v>
+        <v>545602</v>
       </c>
       <c r="R5" t="n">
-        <v>7207897</v>
+        <v>7207648</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188847</v>
+        <v>113188845</v>
       </c>
       <c r="B18" t="n">
-        <v>74344</v>
+        <v>79223</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545589</v>
+        <v>545634</v>
       </c>
       <c r="R18" t="n">
-        <v>7207713</v>
+        <v>7207917</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2816,10 +2816,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188845</v>
+        <v>113188847</v>
       </c>
       <c r="B21" t="n">
-        <v>79223</v>
+        <v>74344</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2832,21 +2832,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545634</v>
+        <v>545589</v>
       </c>
       <c r="R21" t="n">
-        <v>7207917</v>
+        <v>7207713</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113188854</v>
+        <v>113188900</v>
       </c>
       <c r="B2" t="n">
-        <v>55980</v>
+        <v>74330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545558</v>
+        <v>545658</v>
       </c>
       <c r="R2" t="n">
-        <v>7207771</v>
+        <v>7207904</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113188844</v>
+        <v>113188905</v>
       </c>
       <c r="B3" t="n">
-        <v>79223</v>
+        <v>78164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545582</v>
+        <v>545601</v>
       </c>
       <c r="R3" t="n">
-        <v>7207996</v>
+        <v>7207930</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113188903</v>
+        <v>113188906</v>
       </c>
       <c r="B4" t="n">
-        <v>90101</v>
+        <v>78164</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545662</v>
+        <v>545636</v>
       </c>
       <c r="R4" t="n">
-        <v>7207897</v>
+        <v>7207923</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1014,7 @@
         <v>113188849</v>
       </c>
       <c r="B5" t="n">
-        <v>77139</v>
+        <v>77145</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1127,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113188904</v>
+        <v>113188844</v>
       </c>
       <c r="B6" t="n">
-        <v>78158</v>
+        <v>79229</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1239,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113188912</v>
+        <v>113188854</v>
       </c>
       <c r="B7" t="n">
-        <v>78158</v>
+        <v>55984</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,34 +1251,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545588</v>
+        <v>545558</v>
       </c>
       <c r="R7" t="n">
-        <v>7207712</v>
+        <v>7207771</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113188846</v>
+        <v>113188903</v>
       </c>
       <c r="B8" t="n">
-        <v>79223</v>
+        <v>90107</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545592</v>
+        <v>545662</v>
       </c>
       <c r="R8" t="n">
-        <v>7207729</v>
+        <v>7207897</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188911</v>
+        <v>113188908</v>
       </c>
       <c r="B9" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545598</v>
+        <v>545682</v>
       </c>
       <c r="R9" t="n">
-        <v>7207729</v>
+        <v>7207850</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188833</v>
+        <v>113188929</v>
       </c>
       <c r="B10" t="n">
-        <v>77153</v>
+        <v>79261</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,25 +1587,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>314</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545680</v>
+        <v>545582</v>
       </c>
       <c r="R10" t="n">
-        <v>7207851</v>
+        <v>7207994</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188834</v>
+        <v>113188902</v>
       </c>
       <c r="B11" t="n">
-        <v>74339</v>
+        <v>90107</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,21 +1703,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,7 +1730,7 @@
         <v>545601</v>
       </c>
       <c r="R11" t="n">
-        <v>7207647</v>
+        <v>7207930</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188840</v>
+        <v>113188912</v>
       </c>
       <c r="B12" t="n">
-        <v>55988</v>
+        <v>78164</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,47 +1811,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545625</v>
+        <v>545588</v>
       </c>
       <c r="R12" t="n">
-        <v>7207808</v>
+        <v>7207712</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1883,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188902</v>
+        <v>113188847</v>
       </c>
       <c r="B13" t="n">
-        <v>90101</v>
+        <v>74350</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,21 +1927,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1960,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545601</v>
+        <v>545589</v>
       </c>
       <c r="R13" t="n">
-        <v>7207930</v>
+        <v>7207713</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1995,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188907</v>
+        <v>113188842</v>
       </c>
       <c r="B14" t="n">
-        <v>78158</v>
+        <v>79255</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,25 +2035,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2072,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545658</v>
+        <v>545634</v>
       </c>
       <c r="R14" t="n">
-        <v>7207904</v>
+        <v>7207920</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2107,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188900</v>
+        <v>113188840</v>
       </c>
       <c r="B15" t="n">
-        <v>74324</v>
+        <v>55992</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,34 +2151,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6439</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545658</v>
+        <v>545625</v>
       </c>
       <c r="R15" t="n">
-        <v>7207904</v>
+        <v>7207808</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188842</v>
+        <v>113188834</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>74345</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,25 +2268,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545634</v>
+        <v>545601</v>
       </c>
       <c r="R16" t="n">
-        <v>7207920</v>
+        <v>7207647</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188909</v>
+        <v>113188833</v>
       </c>
       <c r="B17" t="n">
-        <v>78158</v>
+        <v>77159</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,21 +2384,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545625</v>
+        <v>545680</v>
       </c>
       <c r="R17" t="n">
-        <v>7207808</v>
+        <v>7207851</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188845</v>
+        <v>113188909</v>
       </c>
       <c r="B18" t="n">
-        <v>79223</v>
+        <v>78164</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,21 +2496,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545634</v>
+        <v>545625</v>
       </c>
       <c r="R18" t="n">
-        <v>7207917</v>
+        <v>7207808</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188906</v>
+        <v>113188846</v>
       </c>
       <c r="B19" t="n">
-        <v>78158</v>
+        <v>79229</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2608,21 +2608,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545636</v>
+        <v>545592</v>
       </c>
       <c r="R19" t="n">
-        <v>7207923</v>
+        <v>7207729</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2704,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188908</v>
+        <v>113188907</v>
       </c>
       <c r="B20" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545682</v>
+        <v>545658</v>
       </c>
       <c r="R20" t="n">
-        <v>7207850</v>
+        <v>7207904</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,10 +2816,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188847</v>
+        <v>113188911</v>
       </c>
       <c r="B21" t="n">
-        <v>74344</v>
+        <v>78164</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2832,21 +2832,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545589</v>
+        <v>545598</v>
       </c>
       <c r="R21" t="n">
-        <v>7207713</v>
+        <v>7207729</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188929</v>
+        <v>113188913</v>
       </c>
       <c r="B22" t="n">
-        <v>79255</v>
+        <v>78164</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,20 +2940,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545582</v>
+        <v>545602</v>
       </c>
       <c r="R22" t="n">
-        <v>7207994</v>
+        <v>7207647</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3040,10 +3040,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188913</v>
+        <v>113188845</v>
       </c>
       <c r="B23" t="n">
-        <v>78158</v>
+        <v>79229</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545602</v>
+        <v>545634</v>
       </c>
       <c r="R23" t="n">
-        <v>7207647</v>
+        <v>7207917</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,10 +3152,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188905</v>
+        <v>113188904</v>
       </c>
       <c r="B24" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545601</v>
+        <v>545582</v>
       </c>
       <c r="R24" t="n">
-        <v>7207930</v>
+        <v>7207996</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3262,6 +3262,1704 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>114954297</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78463</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>545868</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7207921</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>114954298</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78463</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>545927</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7207971</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>114954296</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78463</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>545814</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7207856</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>114954286</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79515</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>545827</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7207862</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>114954273</v>
+      </c>
+      <c r="B29" t="n">
+        <v>74605</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>545930</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7207970</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>114954282</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57385</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>545581</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7207789</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>114954287</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79515</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>545869</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7207921</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>114954294</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78463</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>545742</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7207840</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>114954285</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79515</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>545807</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7207871</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>114954288</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79514</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>545742</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7207840</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>114954275</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>545815</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7207858</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>114954291</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56442</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>545827</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7207862</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>114954283</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79515</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>545742</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7207840</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>114954293</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78463</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>545581</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7207788</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>114954299</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78463</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bladberget, Fatsjöluspen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>545970</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7207956</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4960,6 +4960,925 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>115090843</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78476</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bladberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>545452</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7207791</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>115090832</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57388</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bladberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>545355</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7208044</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>115090841</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57346</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bladberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>545332</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7208022</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>115090828</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57239</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Bladberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>545449</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7207797</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>115090839</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79527</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Bladberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>545751</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7207870</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>115090842</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78476</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Bladberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>545757</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7207882</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>115090836</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79528</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bladberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>545751</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7207870</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>115090844</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78476</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Bladberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>545400</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7207811</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5879,6 +5879,586 @@
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>115128441</v>
+      </c>
+      <c r="B48" t="n">
+        <v>56445</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Bladberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>545575</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7207793</v>
+      </c>
+      <c r="S48" t="n">
+        <v>150</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>115128440</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57346</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bladberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>545575</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7207793</v>
+      </c>
+      <c r="S49" t="n">
+        <v>100</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>115128448</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57189</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Bladberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>545575</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7207793</v>
+      </c>
+      <c r="S50" t="n">
+        <v>200</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>115128446</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57388</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bladberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>545575</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7207793</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>115128447</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57841</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Bladberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>545575</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7207793</v>
+      </c>
+      <c r="S52" t="n">
+        <v>150</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48248-2023 artfynd.xlsx
+++ b/artfynd/A 48248-2023 artfynd.xlsx
@@ -5998,7 +5998,7 @@
         <v>115128447</v>
       </c>
       <c r="B49" t="n">
-        <v>57869</v>
+        <v>58013</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
